--- a/examples/fao_a3/corregido/informe.xlsx
+++ b/examples/fao_a3/corregido/informe.xlsx
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>9217.581841240835</v>
+        <v>10084.81227148286</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>2.388462856078723</v>
+        <v>2.281080184364598</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>2304.395460310209</v>
+        <v>2521.203067870716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>9217.581841240835</v>
+        <v>10084.81227148286</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2.388462856078723</v>
+        <v>2.281080184364598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2.346599482965494</v>
+        <v>2.245097357179862</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1866,11 +1866,11 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>3.129783917299089</v>
+        <v>2.989723140356754</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1, 1.5, 2, 2.5, 3</t>
+          <t>1, 1.5, 2, 2.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -1887,11 +1887,11 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3.081435467889235</v>
+        <v>2.943492877017809</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1, 1.5, 2, 2.5, 3</t>
+          <t>1, 1.5, 2, 2.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>warp_total_omits_doors: la resistencia total incluye ROB (Rem!H118 + D190)</t>
+          <t>warp_total_omits_doors: la resistencia total incluye ROB de los dos portones (Rem!H118 + 2·D190)</t>
         </is>
       </c>
     </row>
@@ -6443,7 +6443,7 @@
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>ROB portones [kgf]</t>
+          <t>ROB par de portones [kgf]</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -6520,13 +6520,13 @@
         <v>1.356990427108308</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>17.69858020902099</v>
+        <v>35.39716041804198</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>421.7079375132039</v>
+        <v>439.4065177222249</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>434.951708587351</v>
+        <v>452.6502887963721</v>
       </c>
       <c r="I3" s="5" t="n">
         <v>1395</v>
@@ -6549,13 +6549,13 @@
         <v>3.053228460993694</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>39.82180547029723</v>
+        <v>79.64361094059446</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>646.7792710454542</v>
+        <v>686.6010765157514</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>666.5817358541025</v>
+        <v>706.4035413243997</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>1342.5</v>
@@ -6578,13 +6578,13 @@
         <v>5.427961708433234</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>70.79432083608397</v>
+        <v>141.5886416721679</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>952.9140759446092</v>
+        <v>1023.708396780693</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>981.6020362353377</v>
+        <v>1052.396357071422</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>1290</v>
@@ -6607,13 +6607,13 @@
         <v>8.481190169426929</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>110.6161263063812</v>
+        <v>221.2322526127624</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1334.285575858464</v>
+        <v>1444.901702164846</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1373.993011152582</v>
+        <v>1484.609137458963</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>1237.5</v>
@@ -6636,13 +6636,13 @@
         <v>12.21291384397478</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>159.2872218811889</v>
+        <v>318.5744437623778</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1787.099225051774</v>
+        <v>1946.386446932963</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1839.788025521455</v>
+        <v>1999.075247402643</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>1185</v>
@@ -6665,13 +6665,13 @@
         <v>16.62313273207678</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>216.8076075605071</v>
+        <v>433.6152151210143</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>2304.395460310209</v>
+        <v>2521.203067870716</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>2371.87344601691</v>
+        <v>2588.681053577418</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>1132.5</v>
@@ -6694,13 +6694,13 @@
         <v>21.71184683373293</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>283.1772833443359</v>
+        <v>566.3545666886718</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>2882.969785094818</v>
+        <v>3166.147068439154</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>2966.90642692863</v>
+        <v>3250.083710272965</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>1080</v>
@@ -6723,13 +6723,13 @@
         <v>27.47905614894325</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>358.3962492326751</v>
+        <v>716.7924984653503</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>3519.057486821139</v>
+        <v>3877.453736053814</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>3620.997672160112</v>
+        <v>3979.393921392788</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1027.5</v>
@@ -6752,13 +6752,13 @@
         <v>33.92476067770772</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>442.4645052255249</v>
+        <v>884.9290104510497</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>4209.259347909127</v>
+        <v>4651.723853134651</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>4330.635475739494</v>
+        <v>4773.099980965018</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>975</v>
@@ -7241,7 +7241,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ROB hidrodinámica a 2 kn</t>
+          <t>ROB hidrodinámica de un portón a 2 kn</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ROB hidrodinámica a 3 kn</t>
+          <t>ROB hidrodinámica de un portón a 3 kn</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ROB hidrodinámica a 3.5 kn</t>
+          <t>ROB hidrodinámica de un portón a 3.5 kn</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">

--- a/examples/fao_a3/corregido/informe.xlsx
+++ b/examples/fao_a3/corregido/informe.xlsx
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>20.016988</v>
+        <v>33.481784</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>10084.81227148286</v>
+        <v>10197.79789468776</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>2.281080184364598</v>
+        <v>2.268404949438784</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.02</v>
+        <v>0.05398445558546063</v>
       </c>
       <c r="D14" t="inlineStr"/>
     </row>
@@ -1588,7 +1588,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>2521.203067870716</v>
+        <v>2549.44947367194</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>10084.81227148286</v>
+        <v>10197.79789468776</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2.281080184364598</v>
+        <v>2.268404949438784</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2.245097357179862</v>
+        <v>2.233088292688445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2.989723140356754</v>
+        <v>2.971321229727041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2.943492877017809</v>
+        <v>2.926018967045624</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -2294,7 +2294,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>warp_undersized</t>
+          <t>warp_cd_horizontal_angle</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2304,12 +2304,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>E267:E272</t>
+          <t>E103:E106</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cable de 12 mm (8.55 t) seleccionado con carga mínima requerida de 8.8 t.</t>
+          <t>El CD del cable se toma con la divergencia en planta δ2 = 4.3° (→ 0.02) en vez del ángulo de ataque del cable al flujo, y por la fila más cercana de la tabla, sin interpolar.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2326,22 +2326,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mod_length_wrong_rows</t>
+          <t>warp_undersized</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dimensiones de la Red</t>
+          <t>Cables de Remolque</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>G48</t>
+          <t>E267:E272</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Largo de la red modificada suma filas del plano inferior en vez de la bolsa.</t>
+          <t>Cable de 12 mm (8.55 t) seleccionado con carga mínima requerida de 8.8 t.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2358,7 +2358,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>footrope_mid_truncation</t>
+          <t>mod_length_wrong_rows</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2368,12 +2368,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>F46</t>
+          <t>G48</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MID() sobre números trunca el burlón a 33.3 m (el valor completo es 33.389 m).</t>
+          <t>Largo de la red modificada suma filas del plano inferior en vez de la bolsa.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2390,22 +2390,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>dpa_std_uses_mod_edy</t>
+          <t>footrope_mid_truncation</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mecánica de la Red</t>
+          <t>Dimensiones de la Red</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>P164</t>
+          <t>F46</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>La DPA de Fridman de la red estándar usa el coeficiente Edy de la modificada.</t>
+          <t>MID() sobre números trunca el burlón a 33.3 m (el valor completo es 33.389 m).</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2422,150 +2422,150 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>nomura_column_links_hamuro</t>
+          <t>dpa_std_uses_mod_edy</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Potencia Disponible Arrastre OK</t>
+          <t>Mecánica de la Red</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>G319,G342,G362</t>
+          <t>P164</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>La columna 'Nomura' de los resúmenes enlaza a los resultados de Hamuro.</t>
+          <t>La DPA de Fridman de la red estándar usa el coeficiente Edy de la modificada.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>documentada</t>
+          <t>corregida</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sin conmutador: Nomura se calcula de verdad; el enlace del libro sólo se documenta.</t>
+          <t>Corregida (CORRECTED).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sweep_degrees_of_sine</t>
+          <t>nomura_column_links_hamuro</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Portones y aparejamiento</t>
+          <t>Potencia Disponible Arrastre OK</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>G71</t>
+          <t>G319,G342,G362</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DEGREES(SIN(20)) con el ángulo en grados y error de precedencia.</t>
+          <t>La columna 'Nomura' de los resúmenes enlaza a los resultados de Hamuro.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>corregida</t>
+          <t>documentada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Corregida (CORRECTED).</t>
+          <t>Sin conmutador: Nomura se calcula de verdad; el enlace del libro sólo se documenta.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>nomura_ratio_typo</t>
+          <t>sweep_degrees_of_sine</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tablas de Referencias</t>
+          <t>Portones y aparejamiento</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>G18,G21</t>
+          <t>G71</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Proporción 10.6 donde el resto de la tabla sugiere 1.06.</t>
+          <t>DEGREES(SIN(20)) con el ángulo en grados y error de precedencia.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>reproducida</t>
+          <t>corregida</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tabla de referencia copiada tal cual en ambos modos.</t>
+          <t>Corregida (CORRECTED).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>panel_f_cut_na</t>
+          <t>nomura_ratio_typo</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Paños de red y cortes</t>
+          <t>Tablas de Referencias</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>T122</t>
+          <t>G18,G21</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VLOOKUP/MATCH de la razón de corte del panel F devuelve #N/A.</t>
+          <t>Proporción 10.6 donde el resto de la tabla sugiere 1.06.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>corregida</t>
+          <t>reproducida</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>El código de corte se calcula en ambos modos.</t>
+          <t>Tabla de referencia copiada tal cual en ambos modos.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>codend_minor_side_uses_depth</t>
+          <t>panel_f_cut_na</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mecánica de la Red</t>
+          <t>Paños de red y cortes</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>K36:K37</t>
+          <t>T122</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Lado menor de las bolsas I/J = Paños!H224 (N = 200) en vez de H223 (T2 = 113); infla Ss de 38.75 a 40.90 m² y St de 308.6 a 315.6 m².</t>
+          <t>VLOOKUP/MATCH de la razón de corte del panel F devuelve #N/A.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2575,29 +2575,29 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Corregida (CORRECTED).</t>
+          <t>El código de corte se calcula en ambos modos.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>panel_b_cut_uses_plan_coef</t>
+          <t>codend_minor_side_uses_depth</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Paños de red y cortes</t>
+          <t>Mecánica de la Red</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>S62</t>
+          <t>K36:K37</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>La razón de corte del paño B usa P55 (coeficiente de plano 0.5) en vez de T56 (N).</t>
+          <t>Lado menor de las bolsas I/J = Paños!H224 (N = 200) en vez de H223 (T2 = 113); infla Ss de 38.75 a 40.90 m² y St de 308.6 a 315.6 m².</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2607,14 +2607,14 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>La razón de corte usa N en ambos modos.</t>
+          <t>Corregida (CORRECTED).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>panel_b_cut_code_lookup_a</t>
+          <t>panel_b_cut_uses_plan_coef</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T62</t>
+          <t>S62</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>El código de corte del paño B se busca con la razón del paño A (H63).</t>
+          <t>La razón de corte del paño B usa P55 (coeficiente de plano 0.5) en vez de T56 (N).</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2639,46 +2639,46 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cada paño busca con su propia razón.</t>
+          <t>La razón de corte usa N en ambos modos.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>net_weight_ignores_panel_count</t>
+          <t>panel_b_cut_code_lookup_a</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mecánica de la Red</t>
+          <t>Paños de red y cortes</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>O107,O109</t>
+          <t>T62</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>El peso total suma las filas sin multiplicar por la cantidad de paneles iguales.</t>
+          <t>El código de corte del paño B se busca con la razón del paño A (H63).</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>reproducida</t>
+          <t>corregida</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Peso por fila del libro en ambos modos (documentado).</t>
+          <t>Cada paño busca con su propia razón.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>catenary_ratio_hardcoded</t>
+          <t>net_weight_ignores_panel_count</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2688,91 +2688,123 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>O266</t>
+          <t>O107,O109</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>fL/L = 0.216 fijo (corresponde a DPA/L = 0.87); el DPA/L del modelo (0.45) queda fuera de la tabla de catenaria.</t>
+          <t>El peso total suma las filas sin multiplicar por la cantidad de paneles iguales.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>reproducida</t>
+          <t>corregida</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>fL/L = 0.216 en ambos modos; el valor de tabla se anota en las notas.</t>
+          <t>Corregida (CORRECTED).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>float_lookup_unsorted</t>
+          <t>catenary_ratio_hardcoded</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Flotación y Lastre</t>
+          <t>Mecánica de la Red</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>F92</t>
+          <t>O266</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LOOKUP del diámetro de boya sobre el vector 'cincuenta' sin ordenar.</t>
+          <t>fL/L = 0.216 fijo (corresponde a DPA/L = 0.87); el DPA/L del modelo (0.45) queda fuera de la tabla de catenaria.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>corregida</t>
+          <t>reproducida</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Corregida (CORRECTED).</t>
+          <t>fL/L = 0.216 en ambos modos; el valor de tabla se anota en las notas.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>float_lookup_unsorted</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Flotación y Lastre</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>F92</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LOOKUP del diámetro de boya sobre el vector 'cincuenta' sin ordenar.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>corregida</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Corregida (CORRECTED).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>flotation_rounding_inconsistent</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Flotación y Lastre</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>M43:M50</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>ROUNDDOWN sólo en M42 y en el bloque de 180 HP; el resto de la columna sin redondear.</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>corregida</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Corregida (CORRECTED).</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Celdas del libro: trawlkit.compat.ERRATA; docs/erratas.md</t>
         </is>
@@ -3350,7 +3382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="2" max="2"/>
@@ -3395,6 +3427,16 @@
       <c r="B4" t="inlineStr">
         <is>
           <t>warp_total_omits_doors: la resistencia total incluye ROB de los dos portones (Rem!H118 + 2·D190)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>warp_cd_horizontal_angle: CD del cable 0.0540 con α = acos(cos δ1·cos δ2) = 12.80° interpolado (Rem!E106 usa δ2 → 0.02)</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3618,7 @@
         <v>0.4734720000000001</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>0.110592</v>
+        <v>0.4423679999999999</v>
       </c>
     </row>
     <row r="4">
@@ -3636,7 +3678,7 @@
         <v>0.4734720000000001</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>0.110592</v>
+        <v>0.4423679999999999</v>
       </c>
     </row>
     <row r="5">
@@ -3696,7 +3738,7 @@
         <v>4.576896000000001</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>2.138112</v>
+        <v>4.276223999999999</v>
       </c>
     </row>
     <row r="6">
@@ -3756,7 +3798,7 @@
         <v>4.050816</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>1.892352</v>
+        <v>3.784703999999999</v>
       </c>
     </row>
     <row r="7">
@@ -3875,8 +3917,8 @@
       <c r="O8" s="3" t="n">
         <v>1.514496</v>
       </c>
-      <c r="P8" s="4" t="n">
-        <v>0.6201599999999999</v>
+      <c r="P8" s="3" t="n">
+        <v>1.24032</v>
       </c>
     </row>
     <row r="9">
@@ -3936,7 +3978,7 @@
         <v>15.609888</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>6.39198</v>
+        <v>12.78396</v>
       </c>
     </row>
     <row r="10">
@@ -3996,7 +4038,7 @@
         <v>4.294784</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>1.75864</v>
+        <v>3.51728</v>
       </c>
     </row>
     <row r="11">
@@ -4311,7 +4353,7 @@
         <v>0.4734720000000001</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>0.110592</v>
+        <v>0.4423679999999999</v>
       </c>
     </row>
     <row r="4">
@@ -4371,7 +4413,7 @@
         <v>0.4734720000000001</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>0.110592</v>
+        <v>0.4423679999999999</v>
       </c>
     </row>
     <row r="5">
@@ -4431,7 +4473,7 @@
         <v>4.576896000000001</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>2.138112</v>
+        <v>4.276223999999999</v>
       </c>
     </row>
     <row r="6">
@@ -4491,7 +4533,7 @@
         <v>4.050816</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>1.892352</v>
+        <v>3.784703999999999</v>
       </c>
     </row>
     <row r="7">
@@ -4610,8 +4652,8 @@
       <c r="O8" s="3" t="n">
         <v>1.514496</v>
       </c>
-      <c r="P8" s="4" t="n">
-        <v>0.6201599999999999</v>
+      <c r="P8" s="3" t="n">
+        <v>1.24032</v>
       </c>
     </row>
     <row r="9">
@@ -4671,7 +4713,7 @@
         <v>15.609888</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>6.39198</v>
+        <v>12.78396</v>
       </c>
     </row>
     <row r="10">
@@ -4731,7 +4773,7 @@
         <v>4.294784</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>1.75864</v>
+        <v>3.51728</v>
       </c>
     </row>
     <row r="11">
@@ -4791,7 +4833,7 @@
         <v>6.855480000000002</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>3.20256</v>
+        <v>6.40512</v>
       </c>
     </row>
     <row r="13">
@@ -6517,16 +6559,16 @@
         <v>2.446988059294398</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1.356990427108308</v>
+        <v>3.662819472106187</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>35.39716041804198</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>439.4065177222249</v>
+        <v>441.7123467672228</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>452.6502887963721</v>
+        <v>454.95611784137</v>
       </c>
       <c r="I3" s="5" t="n">
         <v>1395</v>
@@ -6546,16 +6588,16 @@
         <v>5.505723133412395</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>3.053228460993694</v>
+        <v>8.24134381223892</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>79.64361094059446</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>686.6010765157514</v>
+        <v>691.7891918669967</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>706.4035413243997</v>
+        <v>711.591656675645</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>1342.5</v>
@@ -6575,16 +6617,16 @@
         <v>9.787952237177592</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>5.427961708433234</v>
+        <v>14.65127788842475</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>141.5886416721679</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1023.708396780693</v>
+        <v>1032.931712960685</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>1052.396357071422</v>
+        <v>1061.619673251413</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>1290</v>
@@ -6604,16 +6646,16 @@
         <v>15.29367537058999</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>8.481190169426929</v>
+        <v>22.89262170066367</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>221.2322526127624</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1444.901702164846</v>
+        <v>1459.313133696083</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1484.609137458963</v>
+        <v>1499.0205689902</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>1237.5</v>
@@ -6633,16 +6675,16 @@
         <v>23.42860907835062</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>12.21291384397478</v>
+        <v>32.96537524895568</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>318.5744437623778</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1946.386446932963</v>
+        <v>1967.138908337944</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1999.075247402643</v>
+        <v>2019.827708807624</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>1185</v>
@@ -6662,16 +6704,16 @@
         <v>31.88894013442168</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>16.62313273207678</v>
+        <v>44.86953853330078</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>433.6152151210143</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>2521.203067870716</v>
+        <v>2549.44947367194</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>2588.681053577418</v>
+        <v>2616.927459378642</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>1132.5</v>
@@ -6691,16 +6733,16 @@
         <v>41.65086058373443</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>21.71184683373293</v>
+        <v>58.60511155369899</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>566.3545666886718</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>3166.147068439154</v>
+        <v>3203.04033315912</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>3250.083710272965</v>
+        <v>3286.976974992931</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>1080</v>
@@ -6720,16 +6762,16 @@
         <v>52.71437042628889</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>27.47905614894325</v>
+        <v>74.17209431015029</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>716.7924984653503</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>3877.453736053814</v>
+        <v>3924.146774215022</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>3979.393921392788</v>
+        <v>4026.086959553995</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1027.5</v>
@@ -6749,16 +6791,16 @@
         <v>65.07946966208507</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>33.92476067770772</v>
+        <v>91.57048680265468</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>884.9290104510497</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>4651.723853134651</v>
+        <v>4709.369579259598</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>4773.099980965018</v>
+        <v>4830.745707089965</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>975</v>
